--- a/docs/fattibilita/Gantt.xlsx
+++ b/docs/fattibilita/Gantt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gcomi\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gcomi\Desktop\focusFlow\docs\fattibilita\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A94E268-7EB2-485A-99D0-A1938A74B6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6DBBD4-B5A5-495D-AE4F-15FFF29A7366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9327F8D6-4F37-4E25-8083-20A17765DC2F}"/>
   </bookViews>
@@ -121,9 +121,6 @@
     <t>Weeks #</t>
   </si>
   <si>
-    <t>PsyPlatform</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Creazione idea progetto</t>
   </si>
   <si>
@@ -236,6 +233,9 @@
   </si>
   <si>
     <t xml:space="preserve">  Zoom con paziente di adhd</t>
+  </si>
+  <si>
+    <t>FocusFlow</t>
   </si>
 </sst>
 </file>
@@ -710,6 +710,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -721,15 +730,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1126,78 +1126,78 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:47" ht="27" customHeight="1">
-      <c r="C2" s="62" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="62"/>
+      <c r="C2" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="65"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="3:47">
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="65"/>
+      <c r="D3" s="61"/>
       <c r="H3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="59" t="str">
+      <c r="I3" s="62" t="str">
         <f>TEXT(I5,"MMM")</f>
         <v>ott</v>
       </c>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="59" t="str">
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="62" t="str">
         <f>TEXT(M5,"MMM")</f>
         <v>nov</v>
       </c>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="61"/>
-      <c r="Q3" s="59" t="str">
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="62" t="str">
         <f>TEXT(Q5,"MMM")</f>
         <v>dic</v>
       </c>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
       <c r="U3" s="7"/>
-      <c r="V3" s="59" t="str">
+      <c r="V3" s="62" t="str">
         <f>TEXT(V5,"MMM")</f>
         <v>gen</v>
       </c>
-      <c r="W3" s="60"/>
-      <c r="X3" s="60"/>
-      <c r="Y3" s="61"/>
-      <c r="Z3" s="59" t="str">
+      <c r="W3" s="63"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="64"/>
+      <c r="Z3" s="62" t="str">
         <f>TEXT(Z5,"MMM")</f>
         <v>feb</v>
       </c>
-      <c r="AA3" s="60"/>
-      <c r="AB3" s="60"/>
-      <c r="AC3" s="61"/>
-      <c r="AD3" s="59" t="str">
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="64"/>
+      <c r="AD3" s="62" t="str">
         <f>TEXT(AD5,"MMM")</f>
         <v>mar</v>
       </c>
-      <c r="AE3" s="60"/>
-      <c r="AF3" s="60"/>
-      <c r="AG3" s="60"/>
+      <c r="AE3" s="63"/>
+      <c r="AF3" s="63"/>
+      <c r="AG3" s="63"/>
       <c r="AH3" s="7"/>
-      <c r="AI3" s="59" t="str">
+      <c r="AI3" s="62" t="str">
         <f>TEXT(AI5,"MMM")</f>
         <v>apr</v>
       </c>
-      <c r="AJ3" s="60"/>
-      <c r="AK3" s="60"/>
-      <c r="AL3" s="61"/>
-      <c r="AM3" s="59" t="str">
+      <c r="AJ3" s="63"/>
+      <c r="AK3" s="63"/>
+      <c r="AL3" s="64"/>
+      <c r="AM3" s="62" t="str">
         <f>TEXT(AM5,"MMM")</f>
         <v>mag</v>
       </c>
-      <c r="AN3" s="60"/>
-      <c r="AO3" s="60"/>
-      <c r="AP3" s="61"/>
+      <c r="AN3" s="63"/>
+      <c r="AO3" s="63"/>
+      <c r="AP3" s="64"/>
       <c r="AQ3" s="6" t="str">
         <f>TEXT(AQ5,"MMM")</f>
         <v>giu</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="8" spans="3:47" ht="21" customHeight="1">
       <c r="C8" s="33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" s="27">
         <v>1</v>
@@ -1609,7 +1609,7 @@
     </row>
     <row r="9" spans="3:47" ht="21" customHeight="1">
       <c r="C9" s="33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="58" t="s">
         <v>11</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="10" spans="3:47" ht="21" customHeight="1">
       <c r="C10" s="33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="58" t="s">
         <v>11</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="11" spans="3:47" ht="21" customHeight="1">
       <c r="C11" s="33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="27">
         <v>1</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="12" spans="3:47" ht="25" customHeight="1">
       <c r="C12" s="35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" s="35"/>
       <c r="E12" s="31"/>
@@ -1861,7 +1861,7 @@
     </row>
     <row r="13" spans="3:47" ht="21" customHeight="1">
       <c r="C13" s="33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="58" t="s">
         <v>12</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="14" spans="3:47" ht="21" customHeight="1">
       <c r="C14" s="33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" s="58" t="s">
         <v>12</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="15" spans="3:47" ht="21" customHeight="1">
       <c r="C15" s="35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" s="58"/>
       <c r="E15" s="27"/>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="16" spans="3:47" ht="21" customHeight="1">
       <c r="C16" s="33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" s="58" t="s">
         <v>12</v>
@@ -2104,7 +2104,7 @@
     </row>
     <row r="17" spans="3:47" ht="21" customHeight="1">
       <c r="C17" s="33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" s="58" t="s">
         <v>11</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="18" spans="3:47" ht="21" customHeight="1">
       <c r="C18" s="33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>11</v>
@@ -2234,7 +2234,7 @@
     </row>
     <row r="19" spans="3:47" ht="21" customHeight="1">
       <c r="C19" s="35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" s="58"/>
       <c r="E19" s="27"/>
@@ -2282,7 +2282,7 @@
     </row>
     <row r="20" spans="3:47" ht="21" customHeight="1">
       <c r="C20" s="33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="58" t="s">
         <v>12</v>
@@ -2347,7 +2347,7 @@
     </row>
     <row r="21" spans="3:47" ht="21" customHeight="1">
       <c r="C21" s="33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" s="58" t="s">
         <v>12</v>
@@ -2412,7 +2412,7 @@
     </row>
     <row r="22" spans="3:47" ht="21" customHeight="1">
       <c r="C22" s="35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D22" s="58"/>
       <c r="E22" s="27"/>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="23" spans="3:47" ht="21" customHeight="1">
       <c r="C23" s="33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D23" s="58" t="s">
         <v>11</v>
@@ -2525,7 +2525,7 @@
     </row>
     <row r="24" spans="3:47" ht="21" customHeight="1">
       <c r="C24" s="33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D24" s="58" t="s">
         <v>12</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="25" spans="3:47" ht="21" customHeight="1">
       <c r="C25" s="33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D25" s="58" t="s">
         <v>11</v>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="26" spans="3:47" ht="21" customHeight="1">
       <c r="C26" s="35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D26" s="58"/>
       <c r="E26" s="27"/>
@@ -2703,7 +2703,7 @@
     </row>
     <row r="27" spans="3:47" ht="21" customHeight="1">
       <c r="C27" s="33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27" s="58" t="s">
         <v>12</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="28" spans="3:47" ht="21" customHeight="1">
       <c r="C28" s="35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D28" s="58"/>
       <c r="E28" s="27"/>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="29" spans="3:47" ht="21" customHeight="1">
       <c r="C29" s="33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D29" s="58" t="s">
         <v>11</v>
@@ -2881,7 +2881,7 @@
     </row>
     <row r="30" spans="3:47" ht="21" customHeight="1">
       <c r="C30" s="35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D30" s="58"/>
       <c r="E30" s="27"/>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="31" spans="3:47" ht="21" customHeight="1">
       <c r="C31" s="33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="58" t="s">
         <v>12</v>
@@ -2994,7 +2994,7 @@
     </row>
     <row r="32" spans="3:47" ht="21" customHeight="1">
       <c r="C32" s="35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D32" s="58"/>
       <c r="E32" s="27"/>
@@ -3042,7 +3042,7 @@
     </row>
     <row r="33" spans="3:47" ht="21" customHeight="1">
       <c r="C33" s="33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D33" s="58" t="s">
         <v>12</v>
@@ -3107,7 +3107,7 @@
     </row>
     <row r="34" spans="3:47" ht="21" customHeight="1">
       <c r="C34" s="35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="27"/>
@@ -3155,7 +3155,7 @@
     </row>
     <row r="35" spans="3:47" ht="21" customHeight="1">
       <c r="C35" s="33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D35" s="58" t="s">
         <v>11</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="36" spans="3:47" ht="21" customHeight="1">
       <c r="C36" s="33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D36" s="58" t="s">
         <v>12</v>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="38" spans="3:47" ht="21" customHeight="1">
       <c r="C38" s="33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D38" s="58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E38" s="27">
         <v>1</v>
@@ -3407,7 +3407,7 @@
     </row>
     <row r="39" spans="3:47" ht="21" customHeight="1">
       <c r="C39" s="33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D39" s="58" t="s">
         <v>11</v>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="41" spans="3:47" ht="21" customHeight="1">
       <c r="C41" s="33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D41" s="58" t="s">
         <v>11</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="42" spans="3:47" ht="21" customHeight="1">
       <c r="C42" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D42" s="58" t="s">
         <v>11</v>
@@ -3659,7 +3659,7 @@
     </row>
     <row r="43" spans="3:47" ht="21" customHeight="1">
       <c r="C43" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D43" s="58" t="s">
         <v>11</v>
@@ -3748,10 +3748,10 @@
       <c r="D47" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="63" t="s">
-        <v>30</v>
-      </c>
-      <c r="F47" s="64"/>
+      <c r="E47" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47" s="60"/>
       <c r="AS47" s="52">
         <f>SUM(AS8:AS43)</f>
         <v>25</v>
@@ -3770,18 +3770,18 @@
       <c r="D48" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E48" s="63" t="s">
-        <v>31</v>
-      </c>
-      <c r="F48" s="64"/>
+      <c r="E48" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="F48" s="60"/>
     </row>
     <row r="49" spans="3:12">
       <c r="C49" s="43"/>
       <c r="D49" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E49" s="63"/>
-      <c r="F49" s="64"/>
+      <c r="E49" s="59"/>
+      <c r="F49" s="60"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
@@ -3791,8 +3791,8 @@
       <c r="D50" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="63"/>
-      <c r="F50" s="64"/>
+      <c r="E50" s="59"/>
+      <c r="F50" s="60"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
@@ -3865,11 +3865,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="C3:D3"/>
     <mergeCell ref="V3:Y3"/>
     <mergeCell ref="Z3:AC3"/>
     <mergeCell ref="C2:D2"/>
@@ -3879,6 +3874,11 @@
     <mergeCell ref="M3:P3"/>
     <mergeCell ref="Q3:T3"/>
     <mergeCell ref="AD3:AG3"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="C3:D3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="E8:E43">
